--- a/docs/Example Files/CRYSS V2.0 Input File Templates/10 Component Mixture.xlsx
+++ b/docs/Example Files/CRYSS V2.0 Input File Templates/10 Component Mixture.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Dev\06 website\idiocratease-iggy.github.io\docs\Example Files\CRYSS V2.0 Input File Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0EF94AE1-1DE9-4F58-9CEC-4E258139FAAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BBEDD3F-14A0-4C46-8E3C-AAC55FCCF7BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1065" yWindow="210" windowWidth="48060" windowHeight="15030" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3144" yWindow="480" windowWidth="31980" windowHeight="16116" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="slice_records" sheetId="1" r:id="rId1"/>
+    <sheet name="CRYSS Input File V2.0" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -262,6 +262,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -274,12 +286,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -287,12 +293,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -598,62 +598,62 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AK24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="31" width="14" customWidth="1"/>
     <col min="32" max="32" width="18" customWidth="1"/>
-    <col min="33" max="37" width="12.5703125" customWidth="1"/>
+    <col min="33" max="37" width="12.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A1" s="12"/>
-      <c r="B1" s="11" t="s">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A1" s="8"/>
+      <c r="B1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="10" t="s">
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="M1" s="9"/>
-      <c r="N1" s="9"/>
-      <c r="O1" s="9"/>
-      <c r="P1" s="9"/>
-      <c r="Q1" s="9"/>
-      <c r="R1" s="9"/>
-      <c r="S1" s="9"/>
-      <c r="T1" s="9"/>
-      <c r="U1" s="9"/>
-      <c r="V1" s="8" t="s">
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="W1" s="9"/>
-      <c r="X1" s="9"/>
-      <c r="Y1" s="9"/>
-      <c r="Z1" s="9"/>
-      <c r="AA1" s="9"/>
-      <c r="AB1" s="9"/>
-      <c r="AC1" s="9"/>
-      <c r="AD1" s="9"/>
-      <c r="AE1" s="9"/>
-      <c r="AF1" s="13"/>
-      <c r="AG1" s="14" t="s">
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+      <c r="AF1" s="9"/>
+      <c r="AG1" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="AH1" s="15"/>
-      <c r="AI1" s="15"/>
-      <c r="AJ1" s="15"/>
-      <c r="AK1" s="16"/>
-    </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="AH1" s="17"/>
+      <c r="AI1" s="17"/>
+      <c r="AJ1" s="17"/>
+      <c r="AK1" s="18"/>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+      <c r="A2" s="8" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -746,26 +746,26 @@
       <c r="AE2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="AF2" s="17" t="s">
+      <c r="AF2" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="AG2" s="18" t="s">
+      <c r="AG2" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="AH2" s="18" t="s">
+      <c r="AH2" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="AI2" s="18" t="s">
+      <c r="AI2" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="AJ2" s="18" t="s">
+      <c r="AJ2" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="AK2" s="18" t="s">
+      <c r="AK2" s="11" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -802,7 +802,7 @@
       <c r="AI3" s="6"/>
       <c r="AK3" s="7"/>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B4" s="4"/>
       <c r="C4" s="4"/>
       <c r="D4" s="4"/>
@@ -839,7 +839,7 @@
       <c r="AI4" s="6"/>
       <c r="AK4" s="7"/>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
       <c r="D5" s="4"/>
@@ -876,7 +876,7 @@
       <c r="AI5" s="6"/>
       <c r="AK5" s="7"/>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
       <c r="D6" s="4"/>
@@ -913,7 +913,7 @@
       <c r="AI6" s="6"/>
       <c r="AK6" s="7"/>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
       <c r="D7" s="4"/>
@@ -950,7 +950,7 @@
       <c r="AI7" s="6"/>
       <c r="AK7" s="7"/>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B8" s="4"/>
       <c r="C8" s="4"/>
       <c r="D8" s="4"/>
@@ -987,7 +987,7 @@
       <c r="AI8" s="6"/>
       <c r="AK8" s="7"/>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
       <c r="C9" s="4"/>
       <c r="D9" s="4"/>
@@ -1024,7 +1024,7 @@
       <c r="AI9" s="6"/>
       <c r="AK9" s="7"/>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B10" s="4"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
@@ -1061,7 +1061,7 @@
       <c r="AI10" s="6"/>
       <c r="AK10" s="7"/>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B11" s="4"/>
       <c r="C11" s="4"/>
       <c r="D11" s="4"/>
@@ -1098,7 +1098,7 @@
       <c r="AI11" s="6"/>
       <c r="AK11" s="7"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
       <c r="D12" s="4"/>
@@ -1135,7 +1135,7 @@
       <c r="AI12" s="6"/>
       <c r="AK12" s="7"/>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
@@ -1172,7 +1172,7 @@
       <c r="AI13" s="6"/>
       <c r="AK13" s="7"/>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="4"/>
@@ -1209,7 +1209,7 @@
       <c r="AI14" s="6"/>
       <c r="AK14" s="7"/>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
@@ -1246,7 +1246,7 @@
       <c r="AI15" s="6"/>
       <c r="AK15" s="7"/>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.3">
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="4"/>
@@ -1283,7 +1283,7 @@
       <c r="AI16" s="6"/>
       <c r="AK16" s="7"/>
     </row>
-    <row r="17" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="4"/>
@@ -1320,7 +1320,7 @@
       <c r="AI17" s="6"/>
       <c r="AK17" s="7"/>
     </row>
-    <row r="18" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
       <c r="D18" s="4"/>
@@ -1357,7 +1357,7 @@
       <c r="AI18" s="6"/>
       <c r="AK18" s="7"/>
     </row>
-    <row r="19" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
       <c r="D19" s="4"/>
@@ -1394,7 +1394,7 @@
       <c r="AI19" s="6"/>
       <c r="AK19" s="7"/>
     </row>
-    <row r="20" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
       <c r="D20" s="4"/>
@@ -1431,7 +1431,7 @@
       <c r="AI20" s="6"/>
       <c r="AK20" s="7"/>
     </row>
-    <row r="21" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
       <c r="D21" s="4"/>
@@ -1468,7 +1468,7 @@
       <c r="AI21" s="6"/>
       <c r="AK21" s="7"/>
     </row>
-    <row r="22" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
       <c r="D22" s="4"/>
@@ -1505,7 +1505,7 @@
       <c r="AI22" s="6"/>
       <c r="AK22" s="7"/>
     </row>
-    <row r="23" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
       <c r="D23" s="4"/>
@@ -1542,7 +1542,7 @@
       <c r="AI23" s="6"/>
       <c r="AK23" s="7"/>
     </row>
-    <row r="24" spans="2:37" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:37" x14ac:dyDescent="0.3">
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
       <c r="D24" s="4"/>
